--- a/光伏配储项目/电价数据/2026/金鼎站.xlsx
+++ b/光伏配储项目/电价数据/2026/金鼎站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.54936</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.23355</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.65786</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.91304</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.7777000000000001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.62286</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.45831</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.47317</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.4404</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4293</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.47605</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41489</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.41506</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.41546</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40818</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.44208</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42761</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.40961</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.43192</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43599</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.42894</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.43881</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4637</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.5417999999999999</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.65004</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.54383</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.54545</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.22687</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.5648500000000001</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.5840700000000001</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.26617</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.73026</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.6812</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.7676900000000001</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.6821900000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.27915</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.5222</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.44951</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.38186</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.38866</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.71899</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.69375</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.05856</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.4676</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.58223</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.58717</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.61407</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.6900700000000001</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.67538</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.8425499999999999</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.0456</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5205</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.23854</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.1978</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.63001</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.89439</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.97334</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.03164</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.03574</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.42816</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.78822</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.9899199999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.55114</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.30922</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.05329</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.06907</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.53668</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.20311</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.16749</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.08719</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.7004400000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47918</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42177</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.99686</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.74411</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.97333</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.13229</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53628</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5227000000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50629</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.48642</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50497</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39118</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4792</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.38328</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38773</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.57877</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.83729</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7306</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.47858</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.40815</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.42129</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.74512</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.98129</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.60494</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.04022</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.87785</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.73566</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.57038</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.49288</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.4845</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.5444099999999999</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.82738</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.98666</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.18894</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.22844</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.8939</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.34566</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.98015</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.62193</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.05453</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.8975</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.18817</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.67895</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.5906699999999999</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.5372</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.52867</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.58475</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.80892</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.92567</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.94196</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.73321</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.21884</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.23162</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.18769</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.62454</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.90332</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.19223</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.8297599999999999</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.11478</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.9430499999999999</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.5747</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.91669</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.53355</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.25017</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.6508999999999999</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9251699999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44054</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40824</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33338</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.52055</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5242599999999999</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.57152</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.45907</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.47337</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42701</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.42547</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.44059</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.46003</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47923</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.45036</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40318</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.58672</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.76847</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.0239</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.81868</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.58741</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.62513</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.56975</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6545</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.6118899999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.02365</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.24449</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.5366299999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.98165</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.26496</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.13349</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.92459</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.67828</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.69304</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.90188</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.91295</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.7795599999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.53338</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.45746</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.63567</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.00222</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.85268</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.9165099999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.74805</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.05639</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.90351</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.93362</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.16345</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.17717</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.06902</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.09892</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.12996</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.50029</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.85384</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.89107</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.31091</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.51219</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.90263</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.92349</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.9095599999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.95866</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.97742</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.00626</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.78991</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.64307</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.5936399999999999</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.4703</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34315</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.87039</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.51815</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.57905</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.49319</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.49934</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.7071499999999999</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.42301</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.7411599999999999</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47766</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.37405</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.43072</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.59963</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.6758099999999999</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.8676900000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.9684299999999999</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.09613</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.6621</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.34031</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.62419</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.83838</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.6533</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.98148</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.38965</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.73102</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.70947</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.9003</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.54522</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.15594</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.46503</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.43265</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.5430499999999999</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.78646</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.9274600000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.13271</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.95184</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.78449</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.7431599999999999</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.96065</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.9246</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.9385599999999999</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.18788</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.6436900000000001</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.7422</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.10988</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.8894099999999999</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.7187</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.84516</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.98029</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.03413</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.90508</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.0346</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.11997</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.90588</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.05615</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.42868</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.07451</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.14758</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.1888</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.9927699999999999</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.91347</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.89766</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.87881</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.08052</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.59008</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.46009</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.57897</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31912</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.69978</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.45058</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.42984</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.45896</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.47335</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.25151</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.39304</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.63689</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.75448</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.54591</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.62366</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.6461399999999999</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.7520399999999999</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.62661</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29388</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.48855</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.4876</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.4773</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.52559</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.26476</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24311</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.19604</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.14685</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.16819</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.50861</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.43561</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.44788</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.51834</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.43241</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.42195</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.42013</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.49556</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.45058</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.46075</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.4482</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34262</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.99703</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.7539600000000001</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.77461</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5277000000000001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.51616</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.20128</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.06236</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04314</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04389</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04181</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.03659</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.25595</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0745</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04343</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.25748</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.11171</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04840999999999999</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.00159</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04234</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.26851</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.26274</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.26965</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.14455</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.14882</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.29308</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.15413</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.15613</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.28952</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.42725</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.41766</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.3536</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33261</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.42872</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.20855</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.24434</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.23661</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.26739</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2185</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.26988</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.5797100000000001</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.68269</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.53926</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.5125599999999999</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.54012</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.60991</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.74727</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.21608</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.45662</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.6136</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.60658</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.7094</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.4924</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.46438</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.02335</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.63651</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.57192</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.52622</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.52308</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48008</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.64776</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7719199999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.72396</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.52712</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.65259</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.9279400000000001</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.22853</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.71565</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.24344</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.9438500000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.6677</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.62287</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.19898</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.9031399999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.57506</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.21888</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.60511</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.29271</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.6839700000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7958200000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7876599999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78139</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8764</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49768</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41206</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40598</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45526</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2131</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63934</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5399400000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50598</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46502</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.43404</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44766</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45758</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.46009</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40518</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41116</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45725</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5986399999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43625</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.55545</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66083</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.09408</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.5758300000000001</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.45661</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.51501</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.61505</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.9449099999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.3161</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.27689</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.28861</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5465</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.81379</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.54889</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.61227</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.49576</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.72404</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.70098</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.65343</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.57786</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.51818</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.75828</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.64344</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.25211</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.5256799999999999</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.48133</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.5046</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.48975</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.51346</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.45131</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.48931</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.5107200000000001</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.47751</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.50186</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.50791</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.45415</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.50151</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.5219</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.5962999999999999</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.51248</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.5914700000000001</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.52466</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.5204800000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.53308</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.5031600000000001</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.49884</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4680299999999999</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45956</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.42298</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3598</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47637</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41881</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.45194</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.51125</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.39087</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.48198</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.53089</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.56797</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.66692</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.81775</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.43548</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.02807</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.6714199999999999</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.7581</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.67431</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.62902</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.8577400000000001</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.2351</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.44026</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.6702899999999999</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.67034</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.7041799999999999</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.8694299999999999</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.61424</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.63307</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.5319700000000001</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.61134</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.59284</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.2135</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.19695</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.45521</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.43194</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39683</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.48918</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43249</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.40864</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59674</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.16589</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.47592</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7035800000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7953300000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64977</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58362</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.7205900000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.41021</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.59993</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.62617</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.99322</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.82736</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.53852</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.39941</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.59811</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.39253</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.19978</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.71184</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.07005</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.45335</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.8152999999999999</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.41448</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.29234</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.13288</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.06629</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.03264</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.85634</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.79688</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.54473</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.35993</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.19006</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.50099</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.76497</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.34523</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.65307</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.92936</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.92141</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.7851900000000001</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.88948</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.8411799999999999</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.08578</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.9376100000000001</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.6771900000000001</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.9476</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.44515</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.78047</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.83524</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.94265</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.75637</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.79223</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.42213</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.7387899999999999</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.79937</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.90951</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.7002200000000001</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.6878500000000001</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.63093</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.90023</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.78375</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.15299</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.77464</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.76324</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.6361100000000001</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32511</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.44557</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39786</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.4356</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.41595</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.81508</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.6963200000000001</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.4262</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.40146</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.44275</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.42895</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.44608</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.44793</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.40716</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.42543</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.42844</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.63428</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37216</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40549</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45482</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40592</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45485</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43991</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40872</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.40387</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5438</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39729</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38771</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.5226900000000001</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.28948</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27677</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2664</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.44754</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.47165</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.6722</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.58329</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.6369900000000001</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.86541</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.30132</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.19269</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8683500000000001</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45388</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.43088</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.71186</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.95847</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.19314</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.14477</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.04289</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.54757</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.43196</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49917</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.43751</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.4085299999999999</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41874</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5450499999999999</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.39577</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.46229</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.7202200000000001</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.40433</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.93445</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.92143</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.91015</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.91144</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.60321</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.51657</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9668</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.10817</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.73649</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.03522</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.72044</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.60118</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.59392</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.66119</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.82613</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.33098</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.7830199999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.38792</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.49221</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.08229</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.9030199999999999</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.59347</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.57664</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.61035</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.62373</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.61878</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.5957</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.6202</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.21166</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.65307</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.73501</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.65049</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.65828</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.66646</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.59034</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.70076</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.04386</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.15691</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.64433</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.6528</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.64653</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.72622</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.67637</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.7635599999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.63086</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.68791</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.80902</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.46013</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.33739</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.33927</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.47861</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.99258</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.38438</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.41473</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.70163</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49332</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.49091</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.49744</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29578</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28424</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.87201</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.42104</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.1142</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.91939</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.77663</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45338</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39635</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.44556</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50278</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.47973</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.43834</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.47789</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39315</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34928</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.43508</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.7012699999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.41454</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.49482</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.53694</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.47809</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.39666</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.40851</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.41667</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56732</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.41796</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.44412</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.63254</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44185</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.44287</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40909</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65176</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83184</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47218</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40331</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41701</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.44241</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.52222</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.42358</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.5583400000000001</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.77534</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.78371</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.26479</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.4594</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39683</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.5670299999999999</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.5075500000000001</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.7493300000000001</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.7797999999999999</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.5649299999999999</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50874</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45643</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.04203</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.53076</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.48063</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.12705</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.15396</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.11834</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.12884</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.14283</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.03243</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.20802</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.15623</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.14862</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.16515</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.83948</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19962</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.85422</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.35248</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.92743</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.77532</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.96745</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.7422799999999999</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.19074</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.51891</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.09695</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43618</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42513</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.72823</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.08084</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.94555</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41948</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42438</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.41117</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.42262</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.42396</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40627</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.42162</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.40046</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39813</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42472</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.4215</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40374</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4037</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41748</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45317</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5648</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5032</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45334</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.54648</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4322</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.59479</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.72249</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.59529</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.14149</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.21003</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.54334</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.70942</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.47829</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.20308</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.92464</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.45827</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.44932</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.47185</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.5151399999999999</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.60468</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.00658</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.58527</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.72573</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.55099</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.7464299999999999</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.61245</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.57893</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.10527</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.10647</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.24861</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.03977</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.27093</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.45294</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.59936</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.8916799999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.2059</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.82292</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.1352</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.97525</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.48874</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.4809</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.8598300000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.53912</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45735</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46072</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44371</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.44864</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40321</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.5121</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.8146599999999999</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.55686</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.52918</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.54821</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.9438200000000001</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.49187</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.64169</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.73513</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.8135399999999999</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.95811</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4928</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.13273</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.53934</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.09915</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5500499999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.5791799999999999</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.43105</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.45764</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23093</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.43214</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.45271</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.43341</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.45765</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.51389</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41254</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41809</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.50361</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.47467</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.52737</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38771</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40601</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36412</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.72348</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.04654</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.55845</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.42319</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.41997</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.29599</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.43901</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.30526</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3992</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.43037</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.43501</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.50974</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.43216</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.43521</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39199</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.44913</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.4366</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.48371</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.44757</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.41208</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.45604</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35275</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.7107</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.22478</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.22135</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.26596</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.26621</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.42634</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.21185</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.1659</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.26844</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.27775</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.26643</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.6096200000000001</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.49371</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.26392</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.27619</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.15864</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.2656</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.27796</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.38068</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.37823</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.41322</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.7562300000000001</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.43961</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.02222</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.22648</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.59076</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.60623</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.49088</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.69784</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.68864</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.48653</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.40796</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.41301</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.5161</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.41997</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.40635</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.44252</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.74795</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.43366</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.70012</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.47497</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.10848</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.11193</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.02334</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8670800000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.72013</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.04982</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.42839</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.49192</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.44445</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5191399999999999</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.67067</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.5105</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.48175</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.38443</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.04938</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.6690199999999999</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.67538</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.50613</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.44476</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.78442</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.66738</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.54801</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.67457</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.94341</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.54334</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.5532899999999999</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.5133300000000001</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.00945</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.6702</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.6636599999999999</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.6925</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.7113200000000001</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.9818600000000001</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.5502100000000001</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.7285900000000001</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.56488</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.74688</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.33558</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.34879</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.56375</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.33606</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.50292</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.66926</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.09623</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.9566</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.77873</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.81477</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.26876</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.16828</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.97245</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.7091799999999999</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34311</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5356000000000001</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.75564</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.52752</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.7074</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.7089500000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.53504</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.45433</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.44509</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.41765</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.4109</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.41227</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.41762</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5455599999999999</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.54816</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5001100000000001</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.49565</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.41305</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.45347</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.53316</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.7996</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.98248</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.01725</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.93024</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.01988</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.55361</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.54841</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.9595</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.55601</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.56271</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.56947</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.46812</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.45732</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.23556</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.5209</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55849</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.50015</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.6215700000000001</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.44004</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.9802799999999999</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.5907</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.5216799999999999</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.47526</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.47787</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.46332</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.4789</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.46416</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.5483899999999999</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.5331900000000001</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.53499</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.47827</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.49225</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.48071</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.53365</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.6226799999999999</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.98529</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.88418</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.62821</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.55203</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.04558</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.8079299999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.62512</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.97229</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.63091</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.45762</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.49126</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.47971</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.5138200000000001</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34292</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.49015</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.46009</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.45893</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.44062</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.41468</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3767200000000001</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.59501</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.53539</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.53607</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.81124</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.87375</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.60929</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.85481</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.7774500000000001</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.8369500000000001</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.76264</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.7214700000000001</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.74624</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.73768</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.71161</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.71284</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.5058</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.50481</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.72254</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.5310199999999999</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.72588</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.9478300000000001</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.73629</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.92969</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.48607</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.72939</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.65516</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.72197</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.4899</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.49447</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.51688</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.56567</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.63309</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.61584</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.68502</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.69747</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.67589</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.09523</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.97422</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.9121</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.27866</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.23203</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.90939</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.00967</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.8092</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.66001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.65985</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.7423200000000001</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.58388</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4244</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69231</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.4867</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45854</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.6581399999999999</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.60602</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.57578</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36871</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.6482599999999999</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39178</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.58473</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.6125499999999999</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.4859</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.46604</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.40709</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.7779199999999999</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.67112</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.81429</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.63617</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.82202</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.80488</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.8050900000000001</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.85502</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.86742</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.7885700000000001</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>-0.02428</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.55444</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.58031</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.5818</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.04728</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.52601</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.53475</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.65436</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.55536</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.65812</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.63986</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.67197</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.66069</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.57904</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.03296</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.02024</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.69856</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.77421</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.12603</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.10263</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.92537</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.71567</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.90504</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.05013</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.7154700000000001</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.09147</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.07098</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.42348</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.34479</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.11244</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.11426</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.7690900000000001</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.65984</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.7569</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.41334</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37513</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27102</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.7108300000000001</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43702</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.48387</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.8271900000000001</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.34458</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.02542</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.95563</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.98181</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.02019</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.15569</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.00418</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.88574</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.7045399999999999</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.11395</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.17454</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.17137</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.18621</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.8961699999999999</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.72505</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.13444</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.64952</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.14034</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.37145</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.14017</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.14966</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.13841</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.53167</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.23304</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.5177200000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.5293099999999999</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15599</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.61185</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.55275</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.21489</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.78389</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.07644</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.85762</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.8050499999999999</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.02319</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.09068</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.15502</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.07215</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.08276</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.19643</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.17235</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.20062</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.21804</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.04332</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.1854</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.96936</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.14158</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.12228</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.14916</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.1996</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.2184</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.19884</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.83172</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.5635</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.52927</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.49813</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.49423</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.45121</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37565</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.42913</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.3425</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.33745</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.73041</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.08917</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.46431</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5245299999999999</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.39492</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38236</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.8528300000000001</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.49528</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.56857</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.5846699999999999</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.53843</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.83975</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.6451699999999999</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.8450800000000001</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.05738</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.16585</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.27049</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.26576</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.48805</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.38438</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.15174</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.8602799999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.44084</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.7149800000000001</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.7079099999999999</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.51862</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.85164</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.7567999999999999</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.00913</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.75958</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.58657</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.5505800000000001</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.5132000000000001</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.5735</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.42955</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.6230800000000001</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.50077</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.0942</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.08612</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.3673</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.08119</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.11479</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.10777</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.94598</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.9238099999999999</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.21477</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.95653</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.04469</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.88706</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.93275</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.21482</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.89697</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.47604</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.7891699999999999</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.80879</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56592</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.0926</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.85397</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.8544400000000001</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.56167</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.5565099999999999</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.56065</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51705</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.5561200000000001</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41961</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5230399999999999</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.5025299999999999</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.46095</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.46121</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43951</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41302</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49799</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.50175</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5521</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5250900000000001</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52459</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.5629500000000001</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.18591</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.8902100000000001</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.50868</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.9652500000000001</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.52448</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5678500000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.84454</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.7951900000000001</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.5975900000000001</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.8634400000000001</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.4682</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.53599</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.52718</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.19379</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.7075</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.56274</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.10091</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.55643</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.5601900000000001</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.58609</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.8069299999999999</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.56411</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.81533</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.85678</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.18556</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.80596</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.6890700000000001</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.8248799999999999</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.17998</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.15503</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.13935</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.13789</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.8411000000000001</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.71536</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.5842000000000001</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.62119</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.6257200000000001</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.71663</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.8485199999999999</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.8303200000000001</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.5727300000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.7486699999999999</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.70233</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.09018</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.64439</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.61338</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.5399400000000001</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.58602</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.5968300000000001</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.60441</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.5949</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6170800000000001</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.71758</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70717</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.61005</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.53228</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.5137699999999999</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40858</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
